--- a/test_data/CBC_Master_Sheet.xlsx
+++ b/test_data/CBC_Master_Sheet.xlsx
@@ -452,18 +452,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
@@ -534,12 +534,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>OUTWARD CLEARINGUNIT 101 DEFAULT - ~026ABC123</t>
+          <t>OUTWARD CLEARINGUNIT 101 DEFAULT - ~026ABC001</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>TXN-001</t>
+          <t>REF-H001</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -586,7 +586,7 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>TXN-002</t>
+          <t>REF-H002</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -629,12 +629,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>OUTWARD CLEARINGUNIT 203 DEFAULT - ~026DEF456</t>
+          <t>OUTWARD CLEARINGUNIT 203 DEFAULT - ~026ABC003</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>TXN-003</t>
+          <t>REF-H003</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>INWARD REMITTANCETT REF: 044ABLC7890123 AED 490000 SARAH JOHNSON 45 PARK LANE LONDON</t>
+          <t>INWARD REMITTANCETT REF: 044ABLC7890100 AED 490000 SARAH JOHNSON 45 PARK LANE LONDON</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>TXN-004</t>
+          <t>REF-H004</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -725,12 +725,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>OUTWARD CLEARINGUNIT 305 DEFAULT - ~026GHI789</t>
+          <t>OUTWARD CLEARINGUNIT 305 DEFAULT - ~026ABC005</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>TXN-005</t>
+          <t>REF-H005</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -773,12 +773,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>INWARD REMITTANCETT REF: 20260125001234 AED 375000 NADIA HASSAN IBRAHIM</t>
+          <t>INWARD REMITTANCETT REF: 20260125001000 AED 375000 NADIA HASSAN IBRAHIM</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>TXN-006</t>
+          <t>REF-H006</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -821,12 +821,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>OUTWARD CLEARINGUNIT 407 DEFAULT - ~026JKL012</t>
+          <t>OUTWARD CLEARINGUNIT 407 DEFAULT - ~026ABC007</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>TXN-007</t>
+          <t>REF-H007</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -869,12 +869,12 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>INWARD REMITTANCETT REF: 530P5EB4FCD5AA AED 430000 ELENA PETROVA MOSCOW RUSSIA</t>
+          <t>INWARD REMITTANCETT REF: 530P5EB4FCD500 AED 430000 ELENA PETROVA MOSCOW RUSSIA</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>TXN-008</t>
+          <t>REF-H008</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -917,12 +917,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>OUTWARD CLEARINGUNIT 509 DEFAULT - ~026MNO345</t>
+          <t>OUTWARD CLEARINGUNIT 509 DEFAULT - ~026ABC009</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>TXN-009</t>
+          <t>REF-H009</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -965,12 +965,12 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>INWARD REMITTANCETT REF: 20260215005678 AED 395000 JAMES ROBERT WILSON FLAT 12 CHICAGO USA</t>
+          <t>INWARD REMITTANCETT REF: 20260215005000 AED 395000 JAMES ROBERT WILSON FLAT 12 CHICAGO</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>TXN-010</t>
+          <t>REF-H010</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -999,150 +999,6 @@
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>46073</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>INWARD REMITTANCETT REF: 530P4F86D98E201 AED 56250 AHMED HASSAN AL MAKTOUM PO BOX 12345 DUBAI UAE</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>TXN-011</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>56250</v>
-      </c>
-      <c r="G12" s="4">
-        <f>G11-E12+F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>Ahmed Hassan Al Maktoum</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>46078</v>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>46078</v>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>OUTWARD CLEARINGUNIT 102 DEFAULT - ~026PQR678</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>TXN-012</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>47500</v>
-      </c>
-      <c r="G13" s="4">
-        <f>G12-E13+F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Fatima Abdulrahman Saeed</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>46082</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>IPP Customer CreditIPP 20260301ADC6B981118 AED 61250</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>TXN-013</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>61250</v>
-      </c>
-      <c r="G14" s="4">
-        <f>G13-E14+F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Sarah Johnson</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
